--- a/Excel 3/Planilha 1.xlsx
+++ b/Excel 3/Planilha 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aluno\Documents\GitHub\Ezequiel\Excel 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{82300B89-4212-46B2-A3D9-58FE25EE70FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D43362B2-D083-4EE2-A785-69686401F8DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="8205" firstSheet="2" activeTab="3" xr2:uid="{EAD7E9CC-D28D-4D45-A101-7D5749AE3C9B}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11835" firstSheet="2" activeTab="3" xr2:uid="{EAD7E9CC-D28D-4D45-A101-7D5749AE3C9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Atividade-Trimestral 1" sheetId="1" r:id="rId1"/>
@@ -134,7 +134,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -222,16 +222,7 @@
   </cellStyleXfs>
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -241,36 +232,43 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -595,300 +593,300 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="E3" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="17" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="3">
         <v>6.25</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="3">
         <v>7.25</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="3">
         <v>6</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="3">
         <v>5</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="4">
         <v>20</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="9">
         <f>AVERAGE(B5:E5)</f>
         <v>6.125</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="3">
         <v>4</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="3">
         <v>5.5</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="3">
         <v>6</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="3">
         <v>6</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="4">
         <v>6</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="9">
         <f t="shared" ref="G6:G13" si="0">AVERAGE(B6:E6)</f>
         <v>5.375</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="3">
         <v>6.25</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="3">
         <v>5.25</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="3">
         <v>8.25</v>
       </c>
-      <c r="E7" s="6">
-        <v>7</v>
-      </c>
-      <c r="F7" s="7">
+      <c r="E7" s="3">
+        <v>7</v>
+      </c>
+      <c r="F7" s="4">
         <v>5</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="9">
         <f t="shared" si="0"/>
         <v>6.6875</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="3">
         <v>5.5</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="3">
         <v>8</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="3">
         <v>6.5</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="3">
         <v>7.25</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="4">
         <v>0</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="9">
         <f t="shared" si="0"/>
         <v>6.8125</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="6">
-        <v>7</v>
-      </c>
-      <c r="C9" s="6">
+      <c r="B9" s="3">
+        <v>7</v>
+      </c>
+      <c r="C9" s="3">
         <v>9.5</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="3">
         <v>8.25</v>
       </c>
-      <c r="E9" s="6">
-        <v>7</v>
-      </c>
-      <c r="F9" s="7">
+      <c r="E9" s="3">
+        <v>7</v>
+      </c>
+      <c r="F9" s="4">
         <v>0</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="9">
         <f t="shared" si="0"/>
         <v>7.9375</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="3">
         <v>9.25</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="3">
         <v>8</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="3">
         <v>9</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="3">
         <v>10</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="4">
         <v>2</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="9">
         <f t="shared" si="0"/>
         <v>9.0625</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="3">
         <v>8</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="3">
         <v>9.5</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="3">
         <v>8</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="3">
         <v>8</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="4">
         <v>0</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="9">
         <f t="shared" si="0"/>
         <v>8.375</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="3">
         <v>7.25</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="3">
         <v>8.25</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="3">
         <v>6.5</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="3">
         <v>9.25</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="4">
         <v>2</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="9">
         <f t="shared" si="0"/>
         <v>7.8125</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="3">
         <v>10</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="3">
         <v>8.25</v>
       </c>
-      <c r="D13" s="6">
-        <v>7</v>
-      </c>
-      <c r="E13" s="6">
+      <c r="D13" s="3">
+        <v>7</v>
+      </c>
+      <c r="E13" s="3">
         <v>9.5</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="4">
         <v>0</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="9">
         <f t="shared" si="0"/>
         <v>8.6875</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="10">
         <f>SUM(F5:F13)</f>
         <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="9">
         <f>MAX(G5:G13)</f>
         <v>9.0625</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="9">
         <f>MIN(G5:G13)</f>
         <v>5.375</v>
       </c>
@@ -917,300 +915,300 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="E3" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="17" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="6">
-        <v>7</v>
-      </c>
-      <c r="C5" s="6">
+      <c r="B5" s="3">
+        <v>7</v>
+      </c>
+      <c r="C5" s="3">
         <v>5</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="3">
         <v>5.5</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="3">
         <v>5.5</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="4">
         <v>21</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="11">
         <f>AVERAGE(B5:E5)</f>
         <v>5.75</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="6">
-        <v>7</v>
-      </c>
-      <c r="C6" s="6">
+      <c r="B6" s="3">
+        <v>7</v>
+      </c>
+      <c r="C6" s="3">
         <v>6</v>
       </c>
-      <c r="D6" s="6">
-        <v>7</v>
-      </c>
-      <c r="E6" s="6">
-        <v>7</v>
-      </c>
-      <c r="F6" s="7">
+      <c r="D6" s="3">
+        <v>7</v>
+      </c>
+      <c r="E6" s="3">
+        <v>7</v>
+      </c>
+      <c r="F6" s="4">
         <v>6</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="11">
         <f t="shared" ref="G6:G13" si="0">AVERAGE(B6:E6)</f>
         <v>6.75</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="3">
         <v>8</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="3">
         <v>6</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="3">
         <v>8</v>
       </c>
-      <c r="E7" s="6">
-        <v>7</v>
-      </c>
-      <c r="F7" s="7">
+      <c r="E7" s="3">
+        <v>7</v>
+      </c>
+      <c r="F7" s="4">
         <v>5</v>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="11">
         <f t="shared" si="0"/>
         <v>7.25</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="6">
-        <v>7</v>
-      </c>
-      <c r="C8" s="6">
-        <v>7</v>
-      </c>
-      <c r="D8" s="6">
-        <v>7</v>
-      </c>
-      <c r="E8" s="6">
+      <c r="B8" s="3">
+        <v>7</v>
+      </c>
+      <c r="C8" s="3">
+        <v>7</v>
+      </c>
+      <c r="D8" s="3">
+        <v>7</v>
+      </c>
+      <c r="E8" s="3">
         <v>7.25</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="4">
         <v>0</v>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="11">
         <f t="shared" si="0"/>
         <v>7.0625</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="6">
-        <v>7</v>
-      </c>
-      <c r="C9" s="6">
+      <c r="B9" s="3">
+        <v>7</v>
+      </c>
+      <c r="C9" s="3">
         <v>6</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="3">
         <v>8.25</v>
       </c>
-      <c r="E9" s="6">
-        <v>7</v>
-      </c>
-      <c r="F9" s="7">
+      <c r="E9" s="3">
+        <v>7</v>
+      </c>
+      <c r="F9" s="4">
         <v>0</v>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="11">
         <f t="shared" si="0"/>
         <v>7.0625</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="6">
-        <v>7</v>
-      </c>
-      <c r="C10" s="6">
-        <v>7</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="B10" s="3">
+        <v>7</v>
+      </c>
+      <c r="C10" s="3">
+        <v>7</v>
+      </c>
+      <c r="D10" s="3">
         <v>6</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="3">
         <v>10</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="4">
         <v>2</v>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="11">
         <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="3">
         <v>8</v>
       </c>
-      <c r="C11" s="6">
-        <v>7</v>
-      </c>
-      <c r="D11" s="6">
-        <v>7</v>
-      </c>
-      <c r="E11" s="6">
-        <v>7</v>
-      </c>
-      <c r="F11" s="7">
+      <c r="C11" s="3">
+        <v>7</v>
+      </c>
+      <c r="D11" s="3">
+        <v>7</v>
+      </c>
+      <c r="E11" s="3">
+        <v>7</v>
+      </c>
+      <c r="F11" s="4">
         <v>0</v>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="11">
         <f t="shared" si="0"/>
         <v>7.25</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="3">
         <v>7.25</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="3">
         <v>8</v>
       </c>
-      <c r="D12" s="6">
-        <v>7</v>
-      </c>
-      <c r="E12" s="6">
+      <c r="D12" s="3">
+        <v>7</v>
+      </c>
+      <c r="E12" s="3">
         <v>9.25</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="4">
         <v>2</v>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="11">
         <f t="shared" si="0"/>
         <v>7.875</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="6">
-        <v>7</v>
-      </c>
-      <c r="C13" s="6">
-        <v>7</v>
-      </c>
-      <c r="D13" s="6">
-        <v>7</v>
-      </c>
-      <c r="E13" s="6">
+      <c r="B13" s="3">
+        <v>7</v>
+      </c>
+      <c r="C13" s="3">
+        <v>7</v>
+      </c>
+      <c r="D13" s="3">
+        <v>7</v>
+      </c>
+      <c r="E13" s="3">
         <v>9.5</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="4">
         <v>0</v>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="11">
         <f t="shared" si="0"/>
         <v>7.625</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="10">
         <f>SUM(F5:F13)</f>
         <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="11">
         <f>MAX(G5:G13)</f>
         <v>7.875</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="18">
+      <c r="B17" s="11">
         <f>MIN(G5:G13)</f>
         <v>5.75</v>
       </c>
@@ -1239,300 +1237,300 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="E3" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="17" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="3">
         <v>5</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="3">
         <v>5</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="3">
         <v>4</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="3">
         <v>4</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="4">
         <v>1</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="11">
         <f>AVERAGE(B5:E5)</f>
         <v>4.5</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="3">
         <v>8</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="3">
         <v>6</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="3">
         <v>6</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="3">
         <v>8</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="4">
         <v>2</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="11">
         <f t="shared" ref="G6:G13" si="0">AVERAGE(B6:E6)</f>
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="3">
         <v>6.25</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="3">
         <v>5.25</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="3">
         <v>8.25</v>
       </c>
-      <c r="E7" s="6">
-        <v>7</v>
-      </c>
-      <c r="F7" s="7">
+      <c r="E7" s="3">
+        <v>7</v>
+      </c>
+      <c r="F7" s="4">
         <v>1</v>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="11">
         <f t="shared" si="0"/>
         <v>6.6875</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="3">
         <v>5.5</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="3">
         <v>8</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="3">
         <v>6.5</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="3">
         <v>7.25</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="4">
         <v>2</v>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="11">
         <f t="shared" si="0"/>
         <v>6.8125</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="6">
-        <v>7</v>
-      </c>
-      <c r="C9" s="6">
+      <c r="B9" s="3">
+        <v>7</v>
+      </c>
+      <c r="C9" s="3">
         <v>9.5</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="3">
         <v>8.25</v>
       </c>
-      <c r="E9" s="6">
-        <v>7</v>
-      </c>
-      <c r="F9" s="7">
+      <c r="E9" s="3">
+        <v>7</v>
+      </c>
+      <c r="F9" s="4">
         <v>2</v>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="11">
         <f t="shared" si="0"/>
         <v>7.9375</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="3">
         <v>9.25</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="3">
         <v>8</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="3">
         <v>9</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="3">
         <v>10</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="4">
         <v>1</v>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="11">
         <f t="shared" si="0"/>
         <v>9.0625</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="3">
         <v>8</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="3">
         <v>10</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="3">
         <v>9</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="3">
         <v>9</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="4">
         <v>0</v>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="11">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="3">
         <v>7.25</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="3">
         <v>8.25</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="3">
         <v>6.5</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="3">
         <v>9.25</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="4">
         <v>0</v>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="11">
         <f t="shared" si="0"/>
         <v>7.8125</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="3">
         <v>10</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="3">
         <v>8.25</v>
       </c>
-      <c r="D13" s="6">
-        <v>7</v>
-      </c>
-      <c r="E13" s="6">
+      <c r="D13" s="3">
+        <v>7</v>
+      </c>
+      <c r="E13" s="3">
         <v>9.5</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="4">
         <v>0</v>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="11">
         <f t="shared" si="0"/>
         <v>8.6875</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="10">
         <f>SUM(F5:F13)</f>
         <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="11">
         <f>MAX(G5:G13)</f>
         <v>9.0625</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="18">
+      <c r="B17" s="11">
         <f>MIN(G5:G13)</f>
         <v>4.5</v>
       </c>
@@ -1566,44 +1564,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="5" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1611,23 +1609,23 @@
       <c r="A4" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="13">
         <f>'Atividade-Trimestral 1'!G5</f>
         <v>6.125</v>
       </c>
-      <c r="C4" s="20">
+      <c r="C4" s="13">
         <f>'Atividade-Trimestral 2'!G5</f>
         <v>5.75</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="13">
         <f>'Atividade-Trimestral 3'!G5</f>
         <v>4.5</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="14">
         <f>'Atividade-Trimestral 2'!F5+'Atividade-Trimestral 1'!F5+'Atividade-Trimestral 3'!F5</f>
         <v>42</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="12">
         <f>AVERAGE(B4:D4)</f>
         <v>5.458333333333333</v>
       </c>
@@ -1636,23 +1634,23 @@
       <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="13">
         <f>'Atividade-Trimestral 1'!G6</f>
         <v>5.375</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="13">
         <f>'Atividade-Trimestral 2'!G6</f>
         <v>6.75</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="13">
         <f>'Atividade-Trimestral 3'!G6</f>
         <v>7</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="14">
         <f>'Atividade-Trimestral 2'!F6+'Atividade-Trimestral 1'!F6+'Atividade-Trimestral 3'!F6</f>
         <v>14</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="12">
         <f t="shared" ref="F5:F12" si="0">AVERAGE(B5:D5)</f>
         <v>6.375</v>
       </c>
@@ -1661,23 +1659,23 @@
       <c r="A6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="13">
         <f>'Atividade-Trimestral 1'!G7</f>
         <v>6.6875</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="13">
         <f>'Atividade-Trimestral 2'!G7</f>
         <v>7.25</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="13">
         <f>'Atividade-Trimestral 3'!G7</f>
         <v>6.6875</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="14">
         <f>'Atividade-Trimestral 2'!F7+'Atividade-Trimestral 1'!F7+'Atividade-Trimestral 3'!F7</f>
         <v>11</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="12">
         <f t="shared" si="0"/>
         <v>6.875</v>
       </c>
@@ -1686,23 +1684,23 @@
       <c r="A7" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="13">
         <f>'Atividade-Trimestral 1'!G8</f>
         <v>6.8125</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="13">
         <f>'Atividade-Trimestral 2'!G8</f>
         <v>7.0625</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="13">
         <f>'Atividade-Trimestral 3'!G8</f>
         <v>6.8125</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="14">
         <f>'Atividade-Trimestral 2'!F8+'Atividade-Trimestral 1'!F8+'Atividade-Trimestral 3'!F8</f>
         <v>2</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="12">
         <f t="shared" si="0"/>
         <v>6.895833333333333</v>
       </c>
@@ -1711,23 +1709,23 @@
       <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="13">
         <f>'Atividade-Trimestral 1'!G9</f>
         <v>7.9375</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="13">
         <f>'Atividade-Trimestral 2'!G9</f>
         <v>7.0625</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="13">
         <f>'Atividade-Trimestral 3'!G9</f>
         <v>7.9375</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="14">
         <f>'Atividade-Trimestral 2'!F9+'Atividade-Trimestral 1'!F9+'Atividade-Trimestral 3'!F9</f>
         <v>2</v>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="12">
         <f t="shared" si="0"/>
         <v>7.645833333333333</v>
       </c>
@@ -1736,23 +1734,23 @@
       <c r="A9" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="13">
         <f>'Atividade-Trimestral 1'!G10</f>
         <v>9.0625</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="13">
         <f>'Atividade-Trimestral 2'!G10</f>
         <v>7.5</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="13">
         <f>'Atividade-Trimestral 3'!G10</f>
         <v>9.0625</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="14">
         <f>'Atividade-Trimestral 2'!F10+'Atividade-Trimestral 1'!F10+'Atividade-Trimestral 3'!F10</f>
         <v>5</v>
       </c>
-      <c r="F9" s="19">
+      <c r="F9" s="12">
         <f t="shared" si="0"/>
         <v>8.5416666666666661</v>
       </c>
@@ -1761,23 +1759,23 @@
       <c r="A10" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="13">
         <f>'Atividade-Trimestral 1'!G11</f>
         <v>8.375</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="13">
         <f>'Atividade-Trimestral 2'!G11</f>
         <v>7.25</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="13">
         <f>'Atividade-Trimestral 3'!G11</f>
         <v>9</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="14">
         <f>'Atividade-Trimestral 2'!F11+'Atividade-Trimestral 1'!F11+'Atividade-Trimestral 3'!F11</f>
         <v>0</v>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="12">
         <f t="shared" si="0"/>
         <v>8.2083333333333339</v>
       </c>
@@ -1786,23 +1784,23 @@
       <c r="A11" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="20">
+      <c r="B11" s="13">
         <f>'Atividade-Trimestral 1'!G12</f>
         <v>7.8125</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="13">
         <f>'Atividade-Trimestral 2'!G12</f>
         <v>7.875</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="13">
         <f>'Atividade-Trimestral 3'!G12</f>
         <v>7.8125</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="14">
         <f>'Atividade-Trimestral 2'!F12+'Atividade-Trimestral 1'!F12+'Atividade-Trimestral 3'!F12</f>
         <v>4</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="12">
         <f t="shared" si="0"/>
         <v>7.833333333333333</v>
       </c>
@@ -1811,36 +1809,39 @@
       <c r="A12" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="20">
+      <c r="B12" s="13">
         <f>'Atividade-Trimestral 1'!G13</f>
         <v>8.6875</v>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="13">
         <f>'Atividade-Trimestral 2'!G13</f>
         <v>7.625</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="13">
         <f>'Atividade-Trimestral 3'!G13</f>
         <v>8.6875</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="14">
         <f>'Atividade-Trimestral 2'!F13+'Atividade-Trimestral 1'!F13+'Atividade-Trimestral 3'!F13</f>
         <v>0</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="12">
         <f t="shared" si="0"/>
         <v>8.3333333333333339</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="10" t="s">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
+      <c r="E13" s="21">
+        <f>SUM(E4:E12)</f>
+        <v>80</v>
+      </c>
+      <c r="F13" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
